--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -7,8 +7,8 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Contacts Table" sheetId="2" r:id="rId2"/>
-    <x:sheet name="Copy" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Copy From Other" sheetId="5" r:id="rId5"/>
+    <x:sheet name="Copy" sheetId="7" r:id="rId7"/>
+    <x:sheet name="Copy From Other" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -951,9 +951,9 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="3">
-    <x:tablePart r:id="rId7"/>
-    <x:tablePart r:id="rId9"/>
     <x:tablePart r:id="rId10"/>
+    <x:tablePart r:id="rId11"/>
+    <x:tablePart r:id="rId12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1116,9 +1116,9 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="3">
-    <x:tablePart r:id="rId11"/>
-    <x:tablePart r:id="rId12"/>
     <x:tablePart r:id="rId13"/>
+    <x:tablePart r:id="rId14"/>
+    <x:tablePart r:id="rId15"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -1114,7 +1114,14 @@
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
   <x:tableParts count="3">
     <x:tablePart r:id="rId13"/>
     <x:tablePart r:id="rId14"/>
@@ -1223,7 +1230,14 @@
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -80,7 +80,7 @@
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="5">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -90,6 +90,27 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
@@ -289,7 +310,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -335,6 +356,12 @@
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -366,7 +393,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -424,6 +451,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -823,10 +858,10 @@
       <x:c r="D2" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="15" t="s">
+      <x:c r="E2" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="s">
+      <x:c r="F2" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s"/>
@@ -848,10 +883,10 @@
       <x:c r="D3" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="15">
+      <x:c r="E3" s="17">
         <x:v>6961</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="n">
+      <x:c r="F3" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s"/>
@@ -873,10 +908,10 @@
       <x:c r="D4" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E4" s="15">
+      <x:c r="E4" s="17">
         <x:v>2620</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="n">
+      <x:c r="F4" s="18" t="n">
         <x:v>40000</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s"/>
@@ -898,10 +933,10 @@
       <x:c r="D5" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E5" s="15">
+      <x:c r="E5" s="17">
         <x:v>8020</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s"/>
@@ -919,8 +954,8 @@
       </x:c>
       <x:c r="C6" s="0" t="s"/>
       <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="15" t="s"/>
-      <x:c r="F6" s="16" t="n">
+      <x:c r="E6" s="17" t="s"/>
+      <x:c r="F6" s="18" t="n">
         <x:f>SUBTOTAL(109,[Income])</x:f>
       </x:c>
       <x:c r="G6" s="0" t="s"/>
@@ -988,10 +1023,10 @@
       <x:c r="D2" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="15" t="s">
+      <x:c r="E2" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="s">
+      <x:c r="F2" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s"/>
@@ -1013,10 +1048,10 @@
       <x:c r="D3" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="15">
+      <x:c r="E3" s="17">
         <x:v>6961</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="n">
+      <x:c r="F3" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s"/>
@@ -1038,10 +1073,10 @@
       <x:c r="D4" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E4" s="15">
+      <x:c r="E4" s="17">
         <x:v>2620</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="n">
+      <x:c r="F4" s="18" t="n">
         <x:v>40000</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s"/>
@@ -1063,10 +1098,10 @@
       <x:c r="D5" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E5" s="15">
+      <x:c r="E5" s="17">
         <x:v>8020</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s"/>
@@ -1084,8 +1119,8 @@
       </x:c>
       <x:c r="C6" s="0" t="s"/>
       <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="15" t="s"/>
-      <x:c r="F6" s="16">
+      <x:c r="E6" s="17" t="s"/>
+      <x:c r="F6" s="18">
         <x:f>SUBTOTAL(109,[Income])</x:f>
       </x:c>
       <x:c r="G6" s="0" t="s"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -837,15 +837,15 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.410625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.700625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.270625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.550625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.890625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.000625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.440625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.210625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15.410625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.010625000000001" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.270625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.830625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:10">
@@ -1002,15 +1002,15 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.410625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.700625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.270625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.550625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.890625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.000625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.440625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.210625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15.410625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.010625000000001" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.270625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.830625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:10">
@@ -1174,11 +1174,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.270624999999999" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.410625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.700625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.270625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.550625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.980625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.000625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.580625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.280625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -356,10 +356,10 @@
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
@@ -454,11 +454,11 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -356,10 +356,10 @@
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
@@ -454,11 +454,11 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -311,162 +311,162 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="27">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="19">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -843,7 +843,7 @@
     <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.210625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14.010625000000001" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.010625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.830625" style="0" customWidth="1"/>
   </x:cols>
@@ -864,11 +864,9 @@
       <x:c r="F2" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s"/>
       <x:c r="H2" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s"/>
       <x:c r="J2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -889,11 +887,9 @@
       <x:c r="F3" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s"/>
       <x:c r="H3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s"/>
       <x:c r="J3" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -914,11 +910,9 @@
       <x:c r="F4" s="18" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s"/>
       <x:c r="H4" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s"/>
       <x:c r="J4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
@@ -939,11 +933,9 @@
       <x:c r="F5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s"/>
       <x:c r="H5" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I5" s="0" t="s"/>
       <x:c r="J5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -952,25 +944,15 @@
       <x:c r="B6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s"/>
-      <x:c r="D6" s="0" t="s"/>
       <x:c r="E6" s="17" t="s"/>
       <x:c r="F6" s="18" t="n">
         <x:f>SUBTOTAL(109,[Income])</x:f>
       </x:c>
-      <x:c r="G6" s="0" t="s"/>
       <x:c r="H6" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I6" s="0" t="s"/>
-      <x:c r="J6" s="0" t="s"/>
     </x:row>
     <x:row r="7" spans="1:10">
-      <x:c r="B7" s="0" t="s"/>
-      <x:c r="C7" s="0" t="s"/>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
-      <x:c r="F7" s="0" t="s"/>
       <x:c r="H7" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1008,7 +990,7 @@
     <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.210625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14.010625000000001" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.010625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.830625" style="0" customWidth="1"/>
   </x:cols>
@@ -1029,11 +1011,9 @@
       <x:c r="F2" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s"/>
       <x:c r="H2" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s"/>
       <x:c r="J2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -1054,11 +1034,9 @@
       <x:c r="F3" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s"/>
       <x:c r="H3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s"/>
       <x:c r="J3" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -1079,11 +1057,9 @@
       <x:c r="F4" s="18" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s"/>
       <x:c r="H4" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s"/>
       <x:c r="J4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
@@ -1104,11 +1080,9 @@
       <x:c r="F5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s"/>
       <x:c r="H5" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I5" s="0" t="s"/>
       <x:c r="J5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1117,25 +1091,15 @@
       <x:c r="B6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s"/>
-      <x:c r="D6" s="0" t="s"/>
       <x:c r="E6" s="17" t="s"/>
       <x:c r="F6" s="18">
         <x:f>SUBTOTAL(109,[Income])</x:f>
       </x:c>
-      <x:c r="G6" s="0" t="s"/>
       <x:c r="H6" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I6" s="0" t="s"/>
-      <x:c r="J6" s="0" t="s"/>
     </x:row>
     <x:row r="7" spans="1:10">
-      <x:c r="B7" s="0" t="s"/>
-      <x:c r="C7" s="0" t="s"/>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
-      <x:c r="F7" s="0" t="s"/>
       <x:c r="H7" s="0" t="s">
         <x:v>4</x:v>
       </x:c>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -78,7 +78,7 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
+    <x:numFmt numFmtId="165" formatCode="$ #,##0"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -341,7 +341,7 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -353,19 +353,19 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -434,7 +434,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -450,7 +450,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -458,7 +458,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -466,7 +466,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
